--- a/Fit Results/Progressive_fit_nonzero_F1=4.xlsx
+++ b/Fit Results/Progressive_fit_nonzero_F1=4.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wolfwalker\Documents\git\6s7p\Fit Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\Fit Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{0C63A77D-9561-40F4-98C8-445D6DD2FC5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2BEDAB7-9F64-4A3D-9C66-0A214E46D98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{717B8E7C-22B5-4597-83ED-0E167EBD52BD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{717B8E7C-22B5-4597-83ED-0E167EBD52BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Progressive_fit_nonzero_F1=4" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -59,7 +64,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -536,8 +541,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="8"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -925,7 +932,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -933,6 +939,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1882,491 +1889,491 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0531173-3940-4F43-B816-623C0E8A9B32}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="27.26953125" customWidth="1"/>
-    <col min="3" max="3" width="9.1796875" customWidth="1"/>
-    <col min="5" max="5" width="9.7265625" customWidth="1"/>
-    <col min="6" max="6" width="10.453125" customWidth="1"/>
+    <col min="1" max="1" width="27.25" customWidth="1"/>
+    <col min="3" max="3" width="9.125" customWidth="1"/>
+    <col min="5" max="5" width="9.75" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="42.6" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>2.0867800000000001</v>
       </c>
       <c r="C2">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>3.3520000000000001E-2</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="2">
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>2.5060699999999998</v>
       </c>
       <c r="C3">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>4.0329999999999998E-2</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="2">
         <v>4.0000000000000003E-5</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2">
         <v>-3.6999999999999999E-4</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="2">
         <v>-99.235659999999996</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="2">
         <v>1.6240000000000001E-2</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>0.98407999999999995</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>4.0235500000000002</v>
       </c>
       <c r="C4">
         <v>3.8300000000000001E-3</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>6.4570000000000002E-2</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="2">
         <v>6.0000000000000002E-5</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="2">
         <v>9.0000000000000006E-5</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="2">
         <v>146.0256</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="2">
         <v>1.6039999999999999E-2</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>0.32382</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>1.0427900000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>4.0369799999999998</v>
       </c>
       <c r="C5">
         <v>2.8800000000000002E-3</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>6.4829999999999999E-2</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="2">
         <v>6.0000000000000002E-5</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2">
         <v>9.0000000000000006E-5</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="2">
         <v>117.48945000000001</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="2">
         <v>1.6039999999999999E-2</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>0.23783000000000001</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0.69969000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>5.2323599999999999</v>
       </c>
       <c r="C6">
         <v>6.13E-3</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>8.4029999999999994E-2</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="2">
         <v>6.9999999999999994E-5</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2">
         <v>9.0000000000000006E-5</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="2">
         <v>98.86712</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="2">
         <v>1.6039999999999999E-2</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>0.18765999999999999</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0.52747999999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>5.2424400000000002</v>
       </c>
       <c r="C7">
         <v>3.4299999999999999E-3</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>8.3989999999999995E-2</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="2">
         <v>6.9999999999999994E-5</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="2">
         <v>1.7000000000000001E-4</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="2">
         <v>46.035350000000001</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="2">
         <v>1.601E-2</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>0.14927000000000001</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0.88690000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="1">
         <v>8.2047299999999996</v>
       </c>
       <c r="C8">
         <v>3.0960000000000001E-2</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>0.13472999999999999</v>
       </c>
       <c r="E8">
         <v>3.2000000000000003E-4</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>-1E-4</v>
       </c>
       <c r="G8">
         <v>-78.770309999999995</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>1.609E-2</v>
       </c>
       <c r="I8">
         <v>0.14565</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="1">
         <v>6.4958900000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1">
         <v>8.4757200000000008</v>
       </c>
       <c r="C9">
         <v>2.6069999999999999E-2</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>0.14043</v>
       </c>
       <c r="E9">
         <v>1.9000000000000001E-4</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>-4.2000000000000002E-4</v>
       </c>
       <c r="G9">
         <v>-17.9907</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>1.6199999999999999E-2</v>
       </c>
       <c r="I9">
         <v>0.13997999999999999</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="1">
         <v>19.847449999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="1">
         <v>10.65024</v>
       </c>
       <c r="C10">
         <v>1.115E-2</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>0.17312</v>
       </c>
       <c r="E10">
         <v>8.0000000000000007E-5</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>-5.0000000000000001E-4</v>
       </c>
       <c r="G10">
         <v>-12.529199999999999</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>1.6219999999999998E-2</v>
       </c>
       <c r="I10">
         <v>0.10656</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="1">
         <v>20.94228</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="1">
         <v>10.66269</v>
       </c>
       <c r="C11">
         <v>1.54E-2</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>0.17302999999999999</v>
       </c>
       <c r="E11">
         <v>1.6000000000000001E-4</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>-5.0000000000000001E-4</v>
       </c>
       <c r="G11">
         <v>-11.801970000000001</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>1.6219999999999998E-2</v>
       </c>
       <c r="I11">
         <v>9.7850000000000006E-2</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="1">
         <v>19.004270000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="1">
         <v>13.61923</v>
       </c>
       <c r="C12">
         <v>1.172E-2</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>0.21931999999999999</v>
       </c>
       <c r="E12">
         <v>8.0000000000000007E-5</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>-4.2999999999999999E-4</v>
       </c>
       <c r="G12">
         <v>-11.811260000000001</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>1.6199999999999999E-2</v>
       </c>
       <c r="I12">
         <v>7.7030000000000001E-2</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="1">
         <v>19.01925</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="1">
         <v>14.787419999999999</v>
       </c>
       <c r="C13">
         <v>1.864E-2</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>0.24077000000000001</v>
       </c>
       <c r="E13">
         <v>9.0000000000000006E-5</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>-4.6000000000000001E-4</v>
       </c>
       <c r="G13">
         <v>-10.373239999999999</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>1.6209999999999999E-2</v>
       </c>
       <c r="I13">
         <v>7.0319999999999994E-2</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="1">
         <v>19.749559999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="1">
         <v>16.316500000000001</v>
       </c>
       <c r="C14">
         <v>2.3060000000000001E-2</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>0.26506000000000002</v>
       </c>
       <c r="E14">
         <v>1.2E-4</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>-4.6999999999999999E-4</v>
       </c>
       <c r="G14">
         <v>-9.9463799999999996</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>1.6209999999999999E-2</v>
       </c>
       <c r="I14">
         <v>6.5960000000000005E-2</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="1">
         <v>18.62894</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="1">
         <v>18.318529999999999</v>
       </c>
       <c r="C15">
         <v>2.2620000000000001E-2</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>0.30215999999999998</v>
       </c>
       <c r="E15">
         <v>1.2E-4</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>-7.6000000000000004E-4</v>
       </c>
       <c r="G15">
         <v>-5.9021699999999999</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>1.6299999999999999E-2</v>
       </c>
       <c r="I15">
         <v>6.1010000000000002E-2</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="1">
         <v>32.043230000000001</v>
       </c>
     </row>

--- a/Fit Results/Progressive_fit_nonzero_F1=4.xlsx
+++ b/Fit Results/Progressive_fit_nonzero_F1=4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\Fit Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2BEDAB7-9F64-4A3D-9C66-0A214E46D98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6B3D552-3DF6-442D-8BCA-D0FD54CC77FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{717B8E7C-22B5-4597-83ED-0E167EBD52BD}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Number of progressive dat sets</t>
   </si>
@@ -55,9 +55,6 @@
   </si>
   <si>
     <t>Reduced Chi^2</t>
-  </si>
-  <si>
-    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -381,7 +378,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -496,6 +493,86 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -541,10 +618,21 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="6"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="8"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="6" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="6" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="6" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="6" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="6" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="6" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -680,10 +768,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Progressive_fit_nonzero_F1=4'!$B$2:$B$15</c:f>
+              <c:f>'Progressive_fit_nonzero_F1=4'!$B$2:$B$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>2.0867800000000001</c:v>
                 </c:pt>
@@ -691,39 +779,48 @@
                   <c:v>2.5060699999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>3.0580500000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>4.0235500000000002</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>4.0369799999999998</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>5.2323599999999999</c:v>
-                </c:pt>
                 <c:pt idx="5">
+                  <c:v>5.2371400000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>5.2424400000000002</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
+                  <c:v>5.9644599999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.5881400000000001</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>8.2047299999999996</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="10">
                   <c:v>8.4757200000000008</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="11">
                   <c:v>10.65024</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="12">
                   <c:v>10.66269</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="13">
                   <c:v>13.61923</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="14">
                   <c:v>14.787419999999999</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="15">
                   <c:v>16.316500000000001</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="16">
                   <c:v>18.318529999999999</c:v>
                 </c:pt>
               </c:numCache>
@@ -731,10 +828,10 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Progressive_fit_nonzero_F1=4'!$D$2:$D$15</c:f>
+              <c:f>'Progressive_fit_nonzero_F1=4'!$D$2:$D$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>3.3520000000000001E-2</c:v>
                 </c:pt>
@@ -742,39 +839,48 @@
                   <c:v>4.0329999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>4.9050000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>6.4570000000000002E-2</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>6.4829999999999999E-2</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>8.4029999999999994E-2</c:v>
-                </c:pt>
                 <c:pt idx="5">
+                  <c:v>8.4040000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>8.3989999999999995E-2</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
+                  <c:v>9.5439999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.10567</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>0.13472999999999999</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="10">
                   <c:v>0.14043</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="11">
                   <c:v>0.17312</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="12">
                   <c:v>0.17302999999999999</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="13">
                   <c:v>0.21931999999999999</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="14">
                   <c:v>0.24077000000000001</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="15">
                   <c:v>0.26506000000000002</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="16">
                   <c:v>0.30215999999999998</c:v>
                 </c:pt>
               </c:numCache>
@@ -1534,16 +1640,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
+      <xdr:rowOff>269875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>279400</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1888,7 +1994,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0531173-3940-4F43-B816-623C0E8A9B32}">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="27.25" customWidth="1"/>
@@ -1897,7 +2003,7 @@
     <col min="6" max="6" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="42.6" customHeight="1">
+    <row r="1" spans="1:10" ht="42.6" customHeight="1" thickBot="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1930,291 +2036,291 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="3">
         <v>2.0867800000000001</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="4">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="3">
         <v>3.3520000000000001E-2</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="4">
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>10</v>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="7">
         <v>2.5060699999999998</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="8">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="7">
         <v>4.0329999999999998E-2</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="8">
         <v>4.0000000000000003E-5</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="7">
         <v>-3.6999999999999999E-4</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="8">
         <v>-99.235659999999996</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="7">
         <v>1.6240000000000001E-2</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="8">
         <v>0.98407999999999995</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>10</v>
+      <c r="J3" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="1">
-        <v>4.0235500000000002</v>
-      </c>
-      <c r="C4">
-        <v>3.8300000000000001E-3</v>
-      </c>
-      <c r="D4" s="1">
-        <v>6.4570000000000002E-2</v>
-      </c>
-      <c r="E4" s="2">
-        <v>6.0000000000000002E-5</v>
-      </c>
-      <c r="F4" s="2">
-        <v>9.0000000000000006E-5</v>
-      </c>
-      <c r="G4" s="2">
-        <v>146.0256</v>
-      </c>
-      <c r="H4" s="2">
-        <v>1.6039999999999999E-2</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0.32382</v>
-      </c>
-      <c r="J4" s="2">
-        <v>1.0427900000000001</v>
+      <c r="B4" s="7">
+        <v>3.0580500000000002</v>
+      </c>
+      <c r="C4" s="8">
+        <v>1.7799999999999999E-3</v>
+      </c>
+      <c r="D4" s="7">
+        <v>4.9050000000000003E-2</v>
+      </c>
+      <c r="E4" s="8">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="F4" s="7">
+        <v>2.1000000000000001E-4</v>
+      </c>
+      <c r="G4" s="8">
+        <v>94.551010000000005</v>
+      </c>
+      <c r="H4" s="7">
+        <v>1.5990000000000001E-2</v>
+      </c>
+      <c r="I4" s="8">
+        <v>0.47910999999999998</v>
+      </c>
+      <c r="J4" s="9">
+        <v>1.74814</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5">
+      <c r="A5" s="6">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
-        <v>4.0369799999999998</v>
-      </c>
-      <c r="C5">
-        <v>2.8800000000000002E-3</v>
-      </c>
-      <c r="D5" s="1">
-        <v>6.4829999999999999E-2</v>
-      </c>
-      <c r="E5" s="2">
+      <c r="B5" s="7">
+        <v>4.0235500000000002</v>
+      </c>
+      <c r="C5" s="8">
+        <v>3.8300000000000001E-3</v>
+      </c>
+      <c r="D5" s="7">
+        <v>6.4570000000000002E-2</v>
+      </c>
+      <c r="E5" s="8">
         <v>6.0000000000000002E-5</v>
       </c>
-      <c r="F5" s="2">
-        <v>9.0000000000000006E-5</v>
-      </c>
-      <c r="G5" s="2">
-        <v>117.48945000000001</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1.6039999999999999E-2</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0.23783000000000001</v>
-      </c>
-      <c r="J5" s="2">
-        <v>0.69969000000000003</v>
+      <c r="F5" s="7">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="G5" s="8">
+        <v>64.658850000000001</v>
+      </c>
+      <c r="H5" s="7">
+        <v>1.5990000000000001E-2</v>
+      </c>
+      <c r="I5" s="8">
+        <v>0.29810999999999999</v>
+      </c>
+      <c r="J5" s="9">
+        <v>1.19736</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="1">
-        <v>5.2323599999999999</v>
-      </c>
-      <c r="C6">
-        <v>6.13E-3</v>
-      </c>
-      <c r="D6" s="1">
-        <v>8.4029999999999994E-2</v>
-      </c>
-      <c r="E6" s="2">
-        <v>6.9999999999999994E-5</v>
-      </c>
-      <c r="F6" s="2">
-        <v>9.0000000000000006E-5</v>
-      </c>
-      <c r="G6" s="2">
-        <v>98.86712</v>
-      </c>
-      <c r="H6" s="2">
-        <v>1.6039999999999999E-2</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0.18765999999999999</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0.52747999999999995</v>
+      <c r="B6" s="7">
+        <v>4.0369799999999998</v>
+      </c>
+      <c r="C6" s="8">
+        <v>2.8800000000000002E-3</v>
+      </c>
+      <c r="D6" s="7">
+        <v>6.4829999999999999E-2</v>
+      </c>
+      <c r="E6" s="8">
+        <v>6.0000000000000002E-5</v>
+      </c>
+      <c r="F6" s="7">
+        <v>1.7000000000000001E-4</v>
+      </c>
+      <c r="G6" s="8">
+        <v>63.960290000000001</v>
+      </c>
+      <c r="H6" s="7">
+        <v>1.6E-2</v>
+      </c>
+      <c r="I6" s="8">
+        <v>0.23369000000000001</v>
+      </c>
+      <c r="J6" s="9">
+        <v>1.0286299999999999</v>
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7">
+      <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" s="1">
-        <v>5.2424400000000002</v>
-      </c>
-      <c r="C7">
-        <v>3.4299999999999999E-3</v>
-      </c>
-      <c r="D7" s="1">
-        <v>8.3989999999999995E-2</v>
-      </c>
-      <c r="E7" s="2">
+      <c r="B7" s="7">
+        <v>5.2371400000000001</v>
+      </c>
+      <c r="C7" s="8">
+        <v>4.0400000000000002E-3</v>
+      </c>
+      <c r="D7" s="7">
+        <v>8.4040000000000004E-2</v>
+      </c>
+      <c r="E7" s="8">
         <v>6.9999999999999994E-5</v>
       </c>
-      <c r="F7" s="2">
-        <v>1.7000000000000001E-4</v>
-      </c>
-      <c r="G7" s="2">
-        <v>46.035350000000001</v>
-      </c>
-      <c r="H7" s="2">
+      <c r="F7" s="7">
+        <v>1.6000000000000001E-4</v>
+      </c>
+      <c r="G7" s="8">
+        <v>53.170099999999998</v>
+      </c>
+      <c r="H7" s="7">
         <v>1.601E-2</v>
       </c>
-      <c r="I7" s="2">
-        <v>0.14927000000000001</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0.88690000000000002</v>
+      <c r="I7" s="8">
+        <v>0.17118</v>
+      </c>
+      <c r="J7" s="9">
+        <v>0.85877000000000003</v>
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8">
+      <c r="A8" s="6">
         <v>7</v>
       </c>
-      <c r="B8" s="1">
-        <v>8.2047299999999996</v>
-      </c>
-      <c r="C8">
-        <v>3.0960000000000001E-2</v>
-      </c>
-      <c r="D8" s="1">
-        <v>0.13472999999999999</v>
-      </c>
-      <c r="E8">
-        <v>3.2000000000000003E-4</v>
-      </c>
-      <c r="F8" s="1">
-        <v>-1E-4</v>
-      </c>
-      <c r="G8">
-        <v>-78.770309999999995</v>
-      </c>
-      <c r="H8" s="1">
-        <v>1.609E-2</v>
-      </c>
-      <c r="I8">
-        <v>0.14565</v>
-      </c>
-      <c r="J8" s="1">
-        <v>6.4958900000000002</v>
+      <c r="B8" s="7">
+        <v>5.2424400000000002</v>
+      </c>
+      <c r="C8" s="8">
+        <v>3.4299999999999999E-3</v>
+      </c>
+      <c r="D8" s="7">
+        <v>8.3989999999999995E-2</v>
+      </c>
+      <c r="E8" s="8">
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="F8" s="7">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="G8" s="8">
+        <v>42.163290000000003</v>
+      </c>
+      <c r="H8" s="7">
+        <v>1.6E-2</v>
+      </c>
+      <c r="I8" s="8">
+        <v>0.14191999999999999</v>
+      </c>
+      <c r="J8" s="9">
+        <v>0.88275000000000003</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9">
+      <c r="A9" s="6">
         <v>8</v>
       </c>
-      <c r="B9" s="1">
-        <v>8.4757200000000008</v>
-      </c>
-      <c r="C9">
-        <v>2.6069999999999999E-2</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0.14043</v>
-      </c>
-      <c r="E9">
-        <v>1.9000000000000001E-4</v>
-      </c>
-      <c r="F9" s="1">
-        <v>-4.2000000000000002E-4</v>
-      </c>
-      <c r="G9">
-        <v>-17.9907</v>
-      </c>
-      <c r="H9" s="1">
-        <v>1.6199999999999999E-2</v>
-      </c>
-      <c r="I9">
-        <v>0.13997999999999999</v>
-      </c>
-      <c r="J9" s="1">
-        <v>19.847449999999998</v>
+      <c r="B9" s="7">
+        <v>5.9644599999999999</v>
+      </c>
+      <c r="C9" s="8">
+        <v>3.9699999999999996E-3</v>
+      </c>
+      <c r="D9" s="7">
+        <v>9.5439999999999997E-2</v>
+      </c>
+      <c r="E9" s="8">
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="F9" s="7">
+        <v>2.2000000000000001E-4</v>
+      </c>
+      <c r="G9" s="8">
+        <v>30.53237</v>
+      </c>
+      <c r="H9" s="7">
+        <v>1.5980000000000001E-2</v>
+      </c>
+      <c r="I9" s="8">
+        <v>0.11878</v>
+      </c>
+      <c r="J9" s="9">
+        <v>1.1174299999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
-      <c r="A10">
+    <row r="10" spans="1:10" ht="15" thickBot="1">
+      <c r="A10" s="10">
         <v>9</v>
       </c>
-      <c r="B10" s="1">
-        <v>10.65024</v>
-      </c>
-      <c r="C10">
-        <v>1.115E-2</v>
-      </c>
-      <c r="D10" s="1">
-        <v>0.17312</v>
-      </c>
-      <c r="E10">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="F10" s="1">
-        <v>-5.0000000000000001E-4</v>
-      </c>
-      <c r="G10">
-        <v>-12.529199999999999</v>
-      </c>
-      <c r="H10" s="1">
-        <v>1.6219999999999998E-2</v>
-      </c>
-      <c r="I10">
-        <v>0.10656</v>
-      </c>
-      <c r="J10" s="1">
-        <v>20.94228</v>
+      <c r="B10" s="11">
+        <v>6.5881400000000001</v>
+      </c>
+      <c r="C10" s="12">
+        <v>5.4000000000000003E-3</v>
+      </c>
+      <c r="D10" s="11">
+        <v>0.10567</v>
+      </c>
+      <c r="E10" s="12">
+        <v>6.0000000000000002E-5</v>
+      </c>
+      <c r="F10" s="11">
+        <v>2.1000000000000001E-4</v>
+      </c>
+      <c r="G10" s="12">
+        <v>29.752310000000001</v>
+      </c>
+      <c r="H10" s="11">
+        <v>1.5990000000000001E-2</v>
+      </c>
+      <c r="I10" s="12">
+        <v>0.10284</v>
+      </c>
+      <c r="J10" s="13">
+        <v>1.1392100000000001</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -2222,31 +2328,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <v>10.66269</v>
+        <v>8.2047299999999996</v>
       </c>
       <c r="C11">
-        <v>1.54E-2</v>
+        <v>3.0960000000000001E-2</v>
       </c>
       <c r="D11" s="1">
-        <v>0.17302999999999999</v>
+        <v>0.13472999999999999</v>
       </c>
       <c r="E11">
-        <v>1.6000000000000001E-4</v>
+        <v>3.2000000000000003E-4</v>
       </c>
       <c r="F11" s="1">
-        <v>-5.0000000000000001E-4</v>
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="G11">
-        <v>-11.801970000000001</v>
+        <v>338.83938999999998</v>
       </c>
       <c r="H11" s="1">
-        <v>1.6219999999999998E-2</v>
+        <v>1.6049999999999998E-2</v>
       </c>
       <c r="I11">
-        <v>9.7850000000000006E-2</v>
+        <v>0.10172</v>
       </c>
       <c r="J11" s="1">
-        <v>19.004270000000002</v>
+        <v>5.0825100000000001</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -2254,31 +2360,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <v>13.61923</v>
+        <v>8.4757200000000008</v>
       </c>
       <c r="C12">
-        <v>1.172E-2</v>
+        <v>2.6069999999999999E-2</v>
       </c>
       <c r="D12" s="1">
-        <v>0.21931999999999999</v>
+        <v>0.14043</v>
       </c>
       <c r="E12">
-        <v>8.0000000000000007E-5</v>
+        <v>1.9000000000000001E-4</v>
       </c>
       <c r="F12" s="1">
-        <v>-4.2999999999999999E-4</v>
+        <v>-2.5999999999999998E-4</v>
       </c>
       <c r="G12">
-        <v>-11.811260000000001</v>
+        <v>-23.35192</v>
       </c>
       <c r="H12" s="1">
-        <v>1.6199999999999999E-2</v>
+        <v>1.6129999999999999E-2</v>
       </c>
       <c r="I12">
-        <v>7.7030000000000001E-2</v>
+        <v>9.9849999999999994E-2</v>
       </c>
       <c r="J12" s="1">
-        <v>19.01925</v>
+        <v>16.985710000000001</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -2286,31 +2392,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <v>14.787419999999999</v>
+        <v>10.65024</v>
       </c>
       <c r="C13">
-        <v>1.864E-2</v>
+        <v>1.115E-2</v>
       </c>
       <c r="D13" s="1">
-        <v>0.24077000000000001</v>
+        <v>0.17312</v>
       </c>
       <c r="E13">
-        <v>9.0000000000000006E-5</v>
+        <v>8.0000000000000007E-5</v>
       </c>
       <c r="F13" s="1">
-        <v>-4.6000000000000001E-4</v>
+        <v>-4.0999999999999999E-4</v>
       </c>
       <c r="G13">
-        <v>-10.373239999999999</v>
+        <v>-13.469519999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>1.6209999999999999E-2</v>
+        <v>1.618E-2</v>
       </c>
       <c r="I13">
-        <v>7.0319999999999994E-2</v>
+        <v>8.6290000000000006E-2</v>
       </c>
       <c r="J13" s="1">
-        <v>19.749559999999999</v>
+        <v>22.5014</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -2318,31 +2424,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="1">
-        <v>16.316500000000001</v>
+        <v>10.66269</v>
       </c>
       <c r="C14">
-        <v>2.3060000000000001E-2</v>
+        <v>1.54E-2</v>
       </c>
       <c r="D14" s="1">
-        <v>0.26506000000000002</v>
+        <v>0.17302999999999999</v>
       </c>
       <c r="E14">
-        <v>1.2E-4</v>
+        <v>1.6000000000000001E-4</v>
       </c>
       <c r="F14" s="1">
-        <v>-4.6999999999999999E-4</v>
+        <v>-4.0999999999999999E-4</v>
       </c>
       <c r="G14">
-        <v>-9.9463799999999996</v>
+        <v>-12.80373</v>
       </c>
       <c r="H14" s="1">
-        <v>1.6209999999999999E-2</v>
+        <v>1.618E-2</v>
       </c>
       <c r="I14">
-        <v>6.5960000000000005E-2</v>
+        <v>8.183E-2</v>
       </c>
       <c r="J14" s="1">
-        <v>18.62894</v>
+        <v>21.583189999999998</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -2350,31 +2456,127 @@
         <v>14</v>
       </c>
       <c r="B15" s="1">
+        <v>13.61923</v>
+      </c>
+      <c r="C15">
+        <v>1.172E-2</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0.21931999999999999</v>
+      </c>
+      <c r="E15">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="F15" s="1">
+        <v>-4.0000000000000002E-4</v>
+      </c>
+      <c r="G15">
+        <v>-11.6812</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1.617E-2</v>
+      </c>
+      <c r="I15">
+        <v>6.898E-2</v>
+      </c>
+      <c r="J15" s="1">
+        <v>20.421140000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1">
+        <v>14.787419999999999</v>
+      </c>
+      <c r="C16">
+        <v>1.864E-2</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0.24077000000000001</v>
+      </c>
+      <c r="E16">
+        <v>9.0000000000000006E-5</v>
+      </c>
+      <c r="F16" s="1">
+        <v>-4.6000000000000001E-4</v>
+      </c>
+      <c r="G16">
+        <v>-9.8962800000000009</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1.619E-2</v>
+      </c>
+      <c r="I16">
+        <v>6.4210000000000003E-2</v>
+      </c>
+      <c r="J16" s="1">
+        <v>22.212399999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1">
+        <v>16.316500000000001</v>
+      </c>
+      <c r="C17">
+        <v>2.3060000000000001E-2</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0.26506000000000002</v>
+      </c>
+      <c r="E17">
+        <v>1.2E-4</v>
+      </c>
+      <c r="F17" s="1">
+        <v>-4.6000000000000001E-4</v>
+      </c>
+      <c r="G17">
+        <v>-9.4375699999999991</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1.619E-2</v>
+      </c>
+      <c r="I17">
+        <v>6.0940000000000001E-2</v>
+      </c>
+      <c r="J17" s="1">
+        <v>21.576239999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1">
         <v>18.318529999999999</v>
       </c>
-      <c r="C15">
+      <c r="C18">
         <v>2.2620000000000001E-2</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D18" s="1">
         <v>0.30215999999999998</v>
       </c>
-      <c r="E15">
+      <c r="E18">
         <v>1.2E-4</v>
       </c>
-      <c r="F15" s="1">
-        <v>-7.6000000000000004E-4</v>
-      </c>
-      <c r="G15">
-        <v>-5.9021699999999999</v>
-      </c>
-      <c r="H15" s="1">
-        <v>1.6299999999999999E-2</v>
-      </c>
-      <c r="I15">
-        <v>6.1010000000000002E-2</v>
-      </c>
-      <c r="J15" s="1">
-        <v>32.043230000000001</v>
+      <c r="F18" s="1">
+        <v>-7.7999999999999999E-4</v>
+      </c>
+      <c r="G18">
+        <v>-5.4371700000000001</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1.6279999999999999E-2</v>
+      </c>
+      <c r="I18">
+        <v>5.704E-2</v>
+      </c>
+      <c r="J18" s="1">
+        <v>36.333840000000002</v>
       </c>
     </row>
   </sheetData>
